--- a/outputs/tables/llm_vs_human_performance.xlsx
+++ b/outputs/tables/llm_vs_human_performance.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,351 +458,1076 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>gpt-5.1 [T0.5-With-K]</t>
+          <t>openai_gpt-oss-20b [T0.5-With-K]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.66 (0.65 - 0.67) / 0.76 (0.75 - 0.77)</t>
+          <t>0.47 (0.37 - 0.53) / 0.53 (0.43 - 0.60)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.72 (0.70 - 0.76) / 0.78 (0.75 - 0.83)</t>
+          <t>0.43 (0.36 - 0.50) / 0.52 (0.48 - 0.59)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.53 (0.49 - 0.59) / 0.60 (0.55 - 0.66)</t>
+          <t>0.36 (0.33 - 0.38) / 0.44 (0.41 - 0.48)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.64 (0.49 - 0.76) / 0.71 (0.55 - 0.83)</t>
+          <t>0.42 (0.33 - 0.53) / 0.50 (0.41 - 0.60)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>gpt-5.1 [T0.5-No-K]</t>
+          <t>openai_gpt-oss-20b [T0.5-No-K]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.63 (0.60 - 0.65) / 0.73 (0.70 - 0.77)</t>
+          <t>0.43 (0.21 - 0.56) / 0.52 (0.29 - 0.65)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.70 (0.52 - 0.83) / 0.76 (0.59 - 0.87)</t>
+          <t>0.15 (0.14 - 0.16) / 0.25 (0.23 - 0.27)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.48 (0.47 - 0.48) / 0.57 (0.56 - 0.59)</t>
+          <t>0.32 (0.29 - 0.36) / 0.40 (0.34 - 0.43)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.60 (0.47 - 0.83) / 0.69 (0.56 - 0.87)</t>
+          <t>0.30 (0.14 - 0.56) / 0.39 (0.23 - 0.65)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>gpt-5.1 [T0-With-K]</t>
+          <t>openai_gpt-oss-20b [T0-With-K]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.65 / 0.73</t>
+          <t>0.38 / 0.43</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.76 / 0.82</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>0.59 / 0.65</t>
-        </is>
-      </c>
+          <t>0.20 / 0.27</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.67 (0.59 - 0.76) / 0.73 (0.65 - 0.82)</t>
+          <t>0.29 (0.20 - 0.38) / 0.35 (0.27 - 0.43)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>gpt-5.1 [T0-No-K]</t>
+          <t>openai_gpt-oss-20b [T0-No-K]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.64 / 0.73</t>
+          <t>0.21 / 0.28</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.79 / 0.86</t>
+          <t>0.38 / 0.46</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.43 / 0.53</t>
+          <t>0.31 / 0.35</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.62 (0.43 - 0.79) / 0.71 (0.53 - 0.86)</t>
+          <t>0.30 (0.21 - 0.38) / 0.36 (0.28 - 0.46)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>gemini-3-pro-preview [T0.5-With-K]</t>
+          <t>moonshotai_Kimi-K2-Thinking [T0.5-With-K]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.62 (0.59 - 0.64) / 0.72 (0.71 - 0.73)</t>
+          <t>0.58 (0.52 - 0.64) / 0.68 (0.61 - 0.73)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.82 (0.81 - 0.83) / 0.87 (0.86 - 0.87)</t>
+          <t>0.63 (0.57 - 0.70) / 0.74 (0.67 - 0.80)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.46 (0.44 - 0.47) / 0.56 (0.55 - 0.58)</t>
+          <t>0.48 (0.46 - 0.49) / 0.58 (0.56 - 0.61)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.63 (0.44 - 0.83) / 0.72 (0.55 - 0.87)</t>
+          <t>0.56 (0.46 - 0.70) / 0.67 (0.56 - 0.80)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>gemini-3-pro-preview [T0.5-No-K]</t>
+          <t>moonshotai_Kimi-K2-Thinking [T0.5-No-K]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.60 (0.57 - 0.64) / 0.69 (0.68 - 0.71)</t>
+          <t>0.64 (0.60 - 0.71) / 0.71 (0.67 - 0.74)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.77 (0.76 - 0.78) / 0.86 (0.83 - 0.87)</t>
+          <t>0.57 (0.16 - 0.78) / 0.65 (0.25 - 0.87)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.47 (0.41 - 0.52) / 0.54 (0.50 - 0.58)</t>
+          <t>0.34 (0.27 - 0.42) / 0.44 (0.40 - 0.51)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.61 (0.41 - 0.78) / 0.70 (0.50 - 0.87)</t>
+          <t>0.52 (0.16 - 0.78) / 0.60 (0.25 - 0.87)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>gemini-3-pro-preview [T0-With-K]</t>
+          <t>moonshotai_Kimi-K2-Thinking [T0-With-K]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.62 / 0.72</t>
+          <t>0.46 / 0.57</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.83 / 0.87</t>
+          <t>0.64 / 0.74</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.45 / 0.56</t>
+          <t>0.45 / 0.55</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.63 (0.45 - 0.83) / 0.72 (0.56 - 0.87)</t>
+          <t>0.52 (0.45 - 0.64) / 0.62 (0.55 - 0.74)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>gemini-3-pro-preview [T0-No-K]</t>
+          <t>moonshotai_Kimi-K2-Thinking [T0-No-K]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.60 / 0.70</t>
+          <t>0.70 / 0.75</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.77 / 0.85</t>
+          <t>0.46 / 0.56</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.46 / 0.55</t>
+          <t>0.38 / 0.47</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.61 (0.46 - 0.77) / 0.70 (0.55 - 0.85)</t>
+          <t>0.51 (0.38 - 0.70) / 0.59 (0.47 - 0.75)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>deepseek-ai_DeepSeek-R1 [T0.5-With-K]</t>
+          <t>mistral-large-latest [T0.5-With-K]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.39 (0.32 - 0.42) / 0.48 (0.42 - 0.52)</t>
+          <t>0.54 (0.49 - 0.57) / 0.67 (0.62 - 0.69)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.45 (0.41 - 0.50) / 0.54 (0.49 - 0.60)</t>
+          <t>0.63 (0.61 - 0.67) / 0.71 (0.68 - 0.75)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.28 (0.26 - 0.31) / 0.38 (0.37 - 0.38)</t>
+          <t>0.30 (0.29 - 0.32) / 0.42 (0.41 - 0.45)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.37 (0.26 - 0.50) / 0.47 (0.37 - 0.60)</t>
+          <t>0.49 (0.29 - 0.67) / 0.60 (0.41 - 0.75)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>deepseek-ai_DeepSeek-R1 [T0.5-No-K]</t>
+          <t>mistral-large-latest [T0.5-No-K]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.55 (0.48 - 0.63) / 0.61 (0.52 - 0.70)</t>
+          <t>0.60 (0.59 - 0.61) / 0.71 (0.70 - 0.71)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.41 (0.23 - 0.75) / 0.50 (0.32 - 0.84)</t>
+          <t>0.73 (0.72 - 0.75) / 0.82 (0.81 - 0.83)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.41 (0.31 - 0.47) / 0.50 (0.41 - 0.55)</t>
+          <t>0.28 (0.25 - 0.34) / 0.40 (0.37 - 0.45)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.46 (0.23 - 0.75) / 0.54 (0.32 - 0.84)</t>
+          <t>0.54 (0.25 - 0.75) / 0.64 (0.37 - 0.83)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>deepseek-ai_DeepSeek-R1 [T0-With-K]</t>
+          <t>mistral-large-latest [T0-With-K]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0.45 / 0.55</t>
+          <t>0.50 / 0.62</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.35 / 0.43</t>
+          <t>0.71 / 0.77</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.31 / 0.41</t>
+          <t>0.31 / 0.43</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.37 (0.31 - 0.45) / 0.46 (0.41 - 0.55)</t>
+          <t>0.51 (0.31 - 0.71) / 0.61 (0.43 - 0.77)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>deepseek-ai_DeepSeek-R1 [T0-No-K]</t>
+          <t>mistral-large-latest [T0-No-K]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0.63 / 0.69</t>
+          <t>0.60 / 0.70</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.79 / 0.87</t>
+          <t>0.73 / 0.82</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.43 / 0.51</t>
+          <t>0.38 / 0.48</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.62 (0.43 - 0.79) / 0.69 (0.51 - 0.87)</t>
+          <t>0.57 (0.38 - 0.73) / 0.67 (0.48 - 0.82)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Clinicians</t>
+          <t>gpt-5.1 [T0.5-With-K]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0.60 (0.23 - 0.75) / 0.68 (0.37 - 0.83)</t>
+          <t>0.66 (0.65 - 0.67) / 0.76 (0.75 - 0.77)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.70 (0.24 - 0.82) / 0.79 (0.36 - 0.89)</t>
+          <t>0.72 (0.70 - 0.76) / 0.78 (0.75 - 0.83)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.50 (0.26 - 0.73) / 0.58 (0.36 - 0.79)</t>
+          <t>0.53 (0.49 - 0.59) / 0.60 (0.55 - 0.66)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.60 (0.23 - 0.82) / 0.68 (0.36 - 0.89)</t>
+          <t>0.64 (0.49 - 0.76) / 0.71 (0.55 - 0.83)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>gpt-5.1 [T0.5-No-K]</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0.63 (0.60 - 0.65) / 0.73 (0.70 - 0.77)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0.70 (0.52 - 0.83) / 0.76 (0.59 - 0.87)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>0.48 (0.47 - 0.48) / 0.57 (0.56 - 0.59)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0.60 (0.47 - 0.83) / 0.69 (0.56 - 0.87)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>gpt-5.1 [T0-With-K]</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0.65 / 0.73</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0.76 / 0.82</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>0.59 / 0.65</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0.67 (0.59 - 0.76) / 0.73 (0.65 - 0.82)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>gpt-5.1 [T0-No-K]</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0.64 / 0.73</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0.79 / 0.86</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>0.43 / 0.53</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0.62 (0.43 - 0.79) / 0.71 (0.53 - 0.86)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini [T0.5-With-K]</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.52 (0.49 - 0.56) / 0.57 (0.52 - 0.61)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0.50 (0.43 - 0.54) / 0.61 (0.54 - 0.66)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>0.24 (0.23 - 0.25) / 0.31 (0.30 - 0.32)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0.42 (0.23 - 0.56) / 0.50 (0.30 - 0.66)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini [T0.5-No-K]</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.59 (0.55 - 0.62) / 0.65 (0.62 - 0.67)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0.71 (0.69 - 0.73) / 0.82 (0.81 - 0.83)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0.29 (0.28 - 0.31) / 0.35 (0.34 - 0.36)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0.53 (0.28 - 0.73) / 0.61 (0.34 - 0.83)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini [T0-With-K]</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0.46 / 0.52</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0.47 / 0.60</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>0.21 / 0.30</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0.38 (0.21 - 0.47) / 0.47 (0.30 - 0.60)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini [T0-No-K]</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0.66 / 0.70</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0.70 / 0.82</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>0.35 / 0.42</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0.57 (0.35 - 0.70) / 0.65 (0.42 - 0.82)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>gemini-3-pro-preview [T0.5-With-K]</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0.62 (0.59 - 0.64) / 0.72 (0.71 - 0.73)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>0.82 (0.81 - 0.83) / 0.87 (0.86 - 0.87)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>0.46 (0.44 - 0.47) / 0.56 (0.55 - 0.58)</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0.63 (0.44 - 0.83) / 0.72 (0.55 - 0.87)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>gemini-3-pro-preview [T0.5-No-K]</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0.60 (0.57 - 0.64) / 0.69 (0.68 - 0.71)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0.77 (0.76 - 0.78) / 0.86 (0.83 - 0.87)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>0.47 (0.41 - 0.52) / 0.54 (0.50 - 0.58)</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0.61 (0.41 - 0.78) / 0.70 (0.50 - 0.87)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>gemini-3-pro-preview [T0-With-K]</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0.62 / 0.72</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>0.83 / 0.87</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>0.45 / 0.56</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0.63 (0.45 - 0.83) / 0.72 (0.56 - 0.87)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>gemini-3-pro-preview [T0-No-K]</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0.60 / 0.70</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>0.77 / 0.85</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>0.46 / 0.55</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0.61 (0.46 - 0.77) / 0.70 (0.55 - 0.85)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>gemini-2.5-flash [T0.5-With-K]</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>0.53 (0.53 - 0.54) / 0.67 (0.66 - 0.67)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>0.64 (0.60 - 0.67) / 0.72 (0.68 - 0.75)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>0.41 (0.40 - 0.44) / 0.52 (0.50 - 0.53)</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0.53 (0.40 - 0.67) / 0.64 (0.50 - 0.75)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>gemini-2.5-flash [T0.5-No-K]</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>0.64 (0.59 - 0.67) / 0.71 (0.69 - 0.72)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>0.61 (0.35 - 0.77) / 0.72 (0.45 - 0.88)</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>0.48 (0.45 - 0.50) / 0.55 (0.51 - 0.57)</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0.58 (0.35 - 0.77) / 0.66 (0.45 - 0.88)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>gemini-2.5-flash [T0-With-K]</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>0.47 / 0.59</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>0.65 / 0.74</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>0.47 / 0.55</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0.53 (0.47 - 0.65) / 0.63 (0.55 - 0.74)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>gemini-2.5-flash [T0-No-K]</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>0.56 / 0.67</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>0.72 / 0.84</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>0.39 / 0.49</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0.56 (0.39 - 0.72) / 0.67 (0.49 - 0.84)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>deepseek-ai_DeepSeek-R1 [T0.5-With-K]</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0.39 (0.32 - 0.42) / 0.48 (0.42 - 0.52)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>0.45 (0.41 - 0.50) / 0.54 (0.49 - 0.60)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>0.28 (0.26 - 0.31) / 0.38 (0.37 - 0.38)</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0.37 (0.26 - 0.50) / 0.47 (0.37 - 0.60)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>deepseek-ai_DeepSeek-R1 [T0.5-No-K]</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>0.55 (0.48 - 0.63) / 0.61 (0.52 - 0.70)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>0.41 (0.23 - 0.75) / 0.50 (0.32 - 0.84)</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>0.41 (0.31 - 0.47) / 0.50 (0.41 - 0.55)</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0.46 (0.23 - 0.75) / 0.54 (0.32 - 0.84)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>deepseek-ai_DeepSeek-R1 [T0-With-K]</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>0.45 / 0.55</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>0.35 / 0.43</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>0.31 / 0.41</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0.37 (0.31 - 0.45) / 0.46 (0.41 - 0.55)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>deepseek-ai_DeepSeek-R1 [T0-No-K]</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>0.63 / 0.69</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>0.79 / 0.87</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>0.43 / 0.51</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0.62 (0.43 - 0.79) / 0.69 (0.51 - 0.87)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-5 [T0.5-With-K]</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>0.57 (0.53 - 0.59) / 0.67 (0.65 - 0.69)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>0.61 (0.59 - 0.64) / 0.70 (0.68 - 0.73)</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>0.40 (0.40 - 0.41) / 0.51 (0.51 - 0.52)</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0.53 (0.40 - 0.64) / 0.63 (0.51 - 0.73)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-5 [T0.5-No-K]</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>0.58 (0.58 - 0.58) / 0.66 (0.66 - 0.67)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>0.74 (0.74 - 0.75) / 0.84 (0.82 - 0.85)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>0.36 (0.32 - 0.39) / 0.47 (0.43 - 0.52)</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0.56 (0.32 - 0.75) / 0.66 (0.43 - 0.85)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-5 [T0-With-K]</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>0.51 / 0.62</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>0.65 / 0.75</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>0.39 / 0.50</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0.52 (0.39 - 0.65) / 0.62 (0.50 - 0.75)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-5 [T0-No-K]</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>0.58 / 0.67</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>0.75 / 0.85</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>0.39 / 0.53</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0.57 (0.39 - 0.75) / 0.68 (0.53 - 0.85)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Qwen_Qwen3-Next-80B-A3B-Thinking [T0.5-With-K]</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>0.46 (0.44 - 0.48) / 0.55 (0.52 - 0.58)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>0.46 (0.44 - 0.50) / 0.58 (0.56 - 0.61)</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>0.40 (0.37 - 0.43) / 0.47 (0.45 - 0.49)</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0.44 (0.37 - 0.50) / 0.53 (0.45 - 0.61)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Qwen_Qwen3-Next-80B-A3B-Thinking [T0.5-No-K]</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>0.60 (0.58 - 0.62) / 0.67 (0.65 - 0.68)</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>0.73 (0.72 - 0.74) / 0.83 (0.83 - 0.84)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>0.40 (0.37 - 0.45) / 0.47 (0.44 - 0.50)</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0.58 (0.37 - 0.74) / 0.66 (0.44 - 0.84)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Qwen_Qwen3-Next-80B-A3B-Thinking [T0-With-K]</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>0.47 / 0.57</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>0.46 / 0.58</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>0.38 / 0.46</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0.44 (0.38 - 0.47) / 0.54 (0.46 - 0.58)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Qwen_Qwen3-Next-80B-A3B-Thinking [T0-No-K]</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>0.63 / 0.69</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>0.72 / 0.83</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>0.42 / 0.49</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0.59 (0.42 - 0.72) / 0.67 (0.49 - 0.83)</t>
         </is>
       </c>
     </row>
